--- a/Data/veglist.xlsx
+++ b/Data/veglist.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koush\eclipse-workspace\SeleniumStart5\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koush\eclipse-workspace\PageObjectModel5\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F97CEF-6133-44D9-AE57-E39659F0525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECE752A-4875-4912-9942-225A53C7B957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13332" yWindow="1728" windowWidth="8652" windowHeight="7716" activeTab="1" xr2:uid="{61E31C4F-E4D9-438C-B137-D31367D9C45B}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{61E31C4F-E4D9-438C-B137-D31367D9C45B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t xml:space="preserve">veglist </t>
   </si>
@@ -85,25 +85,12 @@
   </si>
   <si>
     <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>https://www.saucedemo.com/inventory.html</t>
-  </si>
-  <si>
-    <t>Expect_Url</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -479,36 +466,36 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="17.109375"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -522,104 +509,66 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="21.109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.77734375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="37.77734375"/>
+    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s" s="0">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
+    </row>
+    <row r="2" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s" s="0">
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s" s="0">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s" s="0">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s" s="0">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>14</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
